--- a/fhir/core/StructureDefinition-dk-core-organization.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}dk-core-organization-mandatory-identifier:Minimum one identifier shall be of type SOR-ID, KOMBIT-ORG-ID or CVR-ID {identifier.where(system='urn:oid:1.2.208.176.1.1' or system='https://kombit.dk/sts/organisation' or system='urn:oid:2.16.840.1.113883.2.24.1.1').exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}dk-core-organization-mandatory-identifier:Minimum one identifier shall be of type SOR-ID, KOMBIT-ORG-ID or CVR-ID {identifier.where(system='urn:oid:1.2.208.176.1.1' or system='https://kombit.dk/sts/organisation' or system='urn:oid:1.3.198' or system='http://cvr.dk').exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -861,7 +861,7 @@
     <t>Organization.identifier:Regionskode.system</t>
   </si>
   <si>
-    <t>http://hl7.dk/fhir/core/CodeSystem/dk-core-regional-subdivision-codes</t>
+    <t>urn:iso:std:iso:3166:-2</t>
   </si>
   <si>
     <t>Organization.identifier:Regionskode.value</t>

--- a/fhir/core/StructureDefinition-dk-core-organization.xlsx
+++ b/fhir/core/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
